--- a/воры/Amazing_Pics_SKU ALL_22.06.2026.xlsx
+++ b/воры/Amazing_Pics_SKU ALL_22.06.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\воры\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A229600-C2C8-4621-8F34-F80924EBF59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E764D7-69EA-4865-A11D-AF47C0520169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2773,9 +2773,6 @@
       <c r="B89" s="15">
         <v>1522019568</v>
       </c>
-      <c r="D89" s="3">
-        <v>4785238499</v>
-      </c>
       <c r="R89" s="8" t="s">
         <v>421</v>
       </c>
@@ -2853,9 +2850,6 @@
       <c r="B96" s="15">
         <v>1522020325</v>
       </c>
-      <c r="C96" s="3">
-        <v>4784527273</v>
-      </c>
       <c r="R96" s="8" t="s">
         <v>421</v>
       </c>
@@ -2955,9 +2949,6 @@
       <c r="B105" s="15">
         <v>1532937945</v>
       </c>
-      <c r="C105" s="3">
-        <v>4784276465</v>
-      </c>
       <c r="R105" s="8" t="s">
         <v>421</v>
       </c>
@@ -3101,9 +3092,6 @@
       <c r="B118" s="15">
         <v>1532940241</v>
       </c>
-      <c r="C118" s="3">
-        <v>4788670109</v>
-      </c>
       <c r="R118" s="8" t="s">
         <v>421</v>
       </c>
@@ -3467,6 +3455,8 @@
       <c r="B151" s="15">
         <v>1625046227</v>
       </c>
+      <c r="C151" s="17"/>
+      <c r="D151" s="17"/>
       <c r="E151" s="17"/>
       <c r="F151" s="17"/>
       <c r="R151" s="8" t="s">
@@ -3480,6 +3470,8 @@
       <c r="B152" s="15">
         <v>1625046247</v>
       </c>
+      <c r="C152" s="17"/>
+      <c r="D152" s="17"/>
       <c r="R152" s="8" t="s">
         <v>421</v>
       </c>
@@ -3491,6 +3483,8 @@
       <c r="B153" s="15">
         <v>1625046385</v>
       </c>
+      <c r="C153" s="17"/>
+      <c r="D153" s="17"/>
       <c r="R153" s="8" t="s">
         <v>421</v>
       </c>
@@ -3502,6 +3496,8 @@
       <c r="B154" s="15">
         <v>1625046276</v>
       </c>
+      <c r="C154" s="17"/>
+      <c r="D154" s="17"/>
       <c r="R154" s="8" t="s">
         <v>421</v>
       </c>
@@ -3513,6 +3509,8 @@
       <c r="B155" s="15">
         <v>1625046309</v>
       </c>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
       <c r="R155" s="8" t="s">
         <v>421</v>
       </c>
@@ -3524,15 +3522,9 @@
       <c r="B156" s="15">
         <v>1625431183</v>
       </c>
-      <c r="C156" s="11">
-        <v>4466043329</v>
-      </c>
-      <c r="D156" s="3">
-        <v>4805925521</v>
-      </c>
-      <c r="E156" s="17">
-        <v>4795622852</v>
-      </c>
+      <c r="C156" s="17"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="17"/>
       <c r="R156" s="8" t="s">
         <v>421</v>
       </c>
@@ -3544,6 +3536,8 @@
       <c r="B157" s="15">
         <v>1625431121</v>
       </c>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
       <c r="R157" s="8" t="s">
         <v>421</v>
       </c>
@@ -3555,6 +3549,8 @@
       <c r="B158" s="15">
         <v>1625431048</v>
       </c>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
       <c r="R158" s="8" t="s">
         <v>421</v>
       </c>
@@ -3566,6 +3562,8 @@
       <c r="B159" s="15">
         <v>1626838878</v>
       </c>
+      <c r="C159" s="17"/>
+      <c r="D159" s="17"/>
       <c r="R159" s="8" t="s">
         <v>421</v>
       </c>
@@ -3577,6 +3575,8 @@
       <c r="B160" s="15">
         <v>1626838871</v>
       </c>
+      <c r="C160" s="17"/>
+      <c r="D160" s="17"/>
       <c r="R160" s="8" t="s">
         <v>421</v>
       </c>
@@ -3588,6 +3588,8 @@
       <c r="B161" s="15">
         <v>1626838489</v>
       </c>
+      <c r="C161" s="17"/>
+      <c r="D161" s="17"/>
       <c r="R161" s="8" t="s">
         <v>421</v>
       </c>
@@ -3919,6 +3921,9 @@
       <c r="B191" s="15">
         <v>1738652878</v>
       </c>
+      <c r="C191" s="3">
+        <v>4784294216</v>
+      </c>
       <c r="R191" s="8" t="s">
         <v>421</v>
       </c>
@@ -4472,9 +4477,6 @@
       <c r="B241" s="15">
         <v>1912202800</v>
       </c>
-      <c r="C241" s="3">
-        <v>4784339707</v>
-      </c>
       <c r="R241" s="7" t="s">
         <v>419</v>
       </c>
@@ -5021,6 +5023,9 @@
       <c r="B287" s="15">
         <v>2449977019</v>
       </c>
+      <c r="C287" s="3">
+        <v>4784313256</v>
+      </c>
       <c r="R287" s="8" t="s">
         <v>421</v>
       </c>
@@ -6227,9 +6232,6 @@
       <c r="B387" s="15">
         <v>3697504479</v>
       </c>
-      <c r="C387" s="3">
-        <v>4784553482</v>
-      </c>
       <c r="R387" s="10" t="s">
         <v>422</v>
       </c>
@@ -6242,9 +6244,6 @@
       <c r="B388" s="15">
         <v>3697504448</v>
       </c>
-      <c r="C388" s="3">
-        <v>4802513984</v>
-      </c>
       <c r="R388" s="10" t="s">
         <v>422</v>
       </c>
@@ -6342,9 +6341,6 @@
       <c r="B396" s="15">
         <v>3697505978</v>
       </c>
-      <c r="C396" s="3">
-        <v>4802302346</v>
-      </c>
       <c r="R396" s="10" t="s">
         <v>422</v>
       </c>
@@ -6428,9 +6424,6 @@
       </c>
       <c r="B403" s="15">
         <v>3697505575</v>
-      </c>
-      <c r="C403" s="3">
-        <v>4802334322</v>
       </c>
       <c r="R403" s="10" t="s">
         <v>422</v>
